--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,30 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17903.39</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20390.66</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13833.44</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4378.55</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17903.39</v>
+        <v>17885.01</v>
       </c>
       <c r="C3" t="n">
-        <v>20390.66</v>
+        <v>20364.45</v>
       </c>
       <c r="D3" t="n">
-        <v>13833.44</v>
+        <v>13819.99</v>
       </c>
       <c r="E3" t="n">
-        <v>4378.55</v>
+        <v>4375.48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,30 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17885.01</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20364.45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13819.99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4375.48</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -542,6 +542,405 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20795</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13984</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C6" t="n">
+        <v>20799</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13976</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C7" t="n">
+        <v>20804</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13970</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C8" t="n">
+        <v>20741</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13929</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20788</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13924</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C10" t="n">
+        <v>20788</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13915</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20609</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13873</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C12" t="n">
+        <v>20668</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13897</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20607</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13862</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20604</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13868</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20657</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13907</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C16" t="n">
+        <v>20729</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13928</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20706</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13928</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C18" t="n">
+        <v>20700</v>
+      </c>
+      <c r="D18" t="n">
+        <v>13915</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C19" t="n">
+        <v>20468</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13835</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C20" t="n">
+        <v>20479</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13833</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20459</v>
+      </c>
+      <c r="D21" t="n">
+        <v>13814</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20345</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13781</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C23" t="n">
+        <v>20252</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13757</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C24" t="n">
+        <v>20256</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13762</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>17859</v>
+      </c>
+      <c r="C25" t="n">
+        <v>20361</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13799</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3929</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -941,6 +941,30 @@
         <v>3929</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>17934.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>20458.65</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13857.19</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4393.21</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -965,6 +965,54 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>17969.28</v>
+      </c>
+      <c r="C27" t="n">
+        <v>20458.44</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13865.76</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4390.88</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>17989.44</v>
+      </c>
+      <c r="C28" t="n">
+        <v>20551.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>13917.95</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4410</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1013,6 +1013,30 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>17982.27</v>
+      </c>
+      <c r="C29" t="n">
+        <v>20568.78</v>
+      </c>
+      <c r="D29" t="n">
+        <v>13924.53</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4416.69</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1037,6 +1037,30 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>17982.27</v>
+      </c>
+      <c r="C30" t="n">
+        <v>20568.78</v>
+      </c>
+      <c r="D30" t="n">
+        <v>13924.53</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4416.69</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17982.27</v>
+        <v>17978.11</v>
       </c>
       <c r="C30" t="n">
-        <v>20568.78</v>
+        <v>20563.85</v>
       </c>
       <c r="D30" t="n">
-        <v>13924.53</v>
+        <v>13921.54</v>
       </c>
       <c r="E30" t="n">
-        <v>4416.69</v>
+        <v>4415.49</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harian" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Harian" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1061,6 +1061,54 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>17986.54</v>
+      </c>
+      <c r="C31" t="n">
+        <v>20572.06</v>
+      </c>
+      <c r="D31" t="n">
+        <v>13925.16</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4417.87</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>18016.49</v>
+      </c>
+      <c r="C32" t="n">
+        <v>20598.82</v>
+      </c>
+      <c r="D32" t="n">
+        <v>13939.82</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4412.48</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1109,6 +1109,30 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>17962.81</v>
+      </c>
+      <c r="C33" t="n">
+        <v>20510.03</v>
+      </c>
+      <c r="D33" t="n">
+        <v>13897.71</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4412.76</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1133,6 +1133,30 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>17962.81</v>
+      </c>
+      <c r="C34" t="n">
+        <v>20510.03</v>
+      </c>
+      <c r="D34" t="n">
+        <v>13897.71</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4412.76</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1140,18 +1140,42 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17962.81</v>
+        <v>18058.21</v>
       </c>
       <c r="C34" t="n">
-        <v>20510.03</v>
+        <v>20611.1</v>
       </c>
       <c r="D34" t="n">
-        <v>13897.71</v>
+        <v>13956.83</v>
       </c>
       <c r="E34" t="n">
-        <v>4412.76</v>
+        <v>4429.76</v>
       </c>
       <c r="F34" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>18099.05</v>
+      </c>
+      <c r="C35" t="n">
+        <v>20688.93</v>
+      </c>
+      <c r="D35" t="n">
+        <v>14002.17</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4439.33</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>exchangerate-api.com</t>
         </is>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1181,6 +1181,78 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>18097.75</v>
+      </c>
+      <c r="C36" t="n">
+        <v>20669.63</v>
+      </c>
+      <c r="D36" t="n">
+        <v>14013.63</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4445.85</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>18090.75</v>
+      </c>
+      <c r="C37" t="n">
+        <v>20663.48</v>
+      </c>
+      <c r="D37" t="n">
+        <v>14009.11</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4444.39</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>18090.75</v>
+      </c>
+      <c r="C38" t="n">
+        <v>20663.48</v>
+      </c>
+      <c r="D38" t="n">
+        <v>14009.11</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4444.39</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1236,18 +1236,66 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18090.75</v>
+        <v>18071.15</v>
       </c>
       <c r="C38" t="n">
-        <v>20663.48</v>
+        <v>20610.58</v>
       </c>
       <c r="D38" t="n">
-        <v>14009.11</v>
+        <v>13982.15</v>
       </c>
       <c r="E38" t="n">
-        <v>4444.39</v>
+        <v>4440.26</v>
       </c>
       <c r="F38" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>18119.39</v>
+      </c>
+      <c r="C39" t="n">
+        <v>20651.14</v>
+      </c>
+      <c r="D39" t="n">
+        <v>14006.11</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4450.23</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>18080.3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>20645.17</v>
+      </c>
+      <c r="D40" t="n">
+        <v>14001.05</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4433.68</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>exchangerate-api.com</t>
         </is>

--- a/data/kurs_valuta.xlsx
+++ b/data/kurs_valuta.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1301,6 +1301,198 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>18074.01</v>
+      </c>
+      <c r="C41" t="n">
+        <v>20693.21</v>
+      </c>
+      <c r="D41" t="n">
+        <v>14012.63</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4435.59</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>17992.31</v>
+      </c>
+      <c r="C42" t="n">
+        <v>20598.37</v>
+      </c>
+      <c r="D42" t="n">
+        <v>13947.17</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4418.1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>17966.85</v>
+      </c>
+      <c r="C43" t="n">
+        <v>20546.53</v>
+      </c>
+      <c r="D43" t="n">
+        <v>13913.29</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4403.51</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>17958.45</v>
+      </c>
+      <c r="C44" t="n">
+        <v>20535.96</v>
+      </c>
+      <c r="D44" t="n">
+        <v>13908.06</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4400.47</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>17944.1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>20507.28</v>
+      </c>
+      <c r="D45" t="n">
+        <v>13888.31</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4382.55</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>17968.1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>20516.73</v>
+      </c>
+      <c r="D46" t="n">
+        <v>13916.96</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4390.54</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>17905.3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>20423.73</v>
+      </c>
+      <c r="D47" t="n">
+        <v>13863.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4378.98</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>17905.3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>20423.73</v>
+      </c>
+      <c r="D48" t="n">
+        <v>13863.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4378.98</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>exchangerate-api.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
